--- a/public/exports/29189919.xlsx
+++ b/public/exports/29189919.xlsx
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100595167</t>
+          <t xml:space="preserve">100377971</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F3">
-        <v>291</v>
+        <v>9582</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -186,11 +186,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F4">
-        <v>548</v>
+        <v>291</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100613718</t>
+          <t xml:space="preserve">100595167</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F5">
-        <v>1750</v>
+        <v>548</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100965432</t>
+          <t xml:space="preserve">100613718</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>771</v>
+        <v>1750</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -336,11 +336,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F7">
-        <v>1602</v>
+        <v>771</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">100965432</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F8">
-        <v>3982</v>
+        <v>1602</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4439751</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F9">
-        <v>280</v>
+        <v>3982</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455442, 100194390</t>
+          <t xml:space="preserve">329181</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F10">
-        <v>1173</v>
+        <v>11385</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">329484, 329485, 329486, 329487, 329488, 329489, 329490, 329491, 329492, 329510, 329493, 329494, 329495, 329496, 329497, 329498, 329499, 329500, 329502, 329503, 329504, 329505, 329506, 329507, 329508, 329509</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>849</v>
+        <v>18167</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">500110, 4464525</t>
+          <t xml:space="preserve">329553, 329554</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F12">
-        <v>2773</v>
+        <v>3790</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">500110, 4464525</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>2650</v>
+        <v>703</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">500111, 4464525</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F14">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704296</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F15">
-        <v>364</v>
+        <v>919</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704296</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F16">
-        <v>364</v>
+        <v>717</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704296</t>
+          <t xml:space="preserve">332592</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F17">
-        <v>1861</v>
+        <v>6642</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704686</t>
+          <t xml:space="preserve">334005, 334006, 334007, 334008, 334009, 334010, 334011, 334012, 334013, 334014, 334015, 334016, 334017, 334018, 334019, 334020, 334021, 334022, 334023, 334024, 334025, 334026, 334027, 334028, 334029, 334030, 334036, 334031, 334032, 334033, 334034, 334035, 334037, 334038, 334039, 334040, 334042, 100319954</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>939</v>
+        <v>9740</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706289</t>
+          <t xml:space="preserve">334871, 334872</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>319</v>
+        <v>2108</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">739159, 5704912</t>
+          <t xml:space="preserve">334947, 334948</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>1046</v>
+        <v>4340</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">739161, 4460928</t>
+          <t xml:space="preserve">4439751</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F21">
-        <v>983</v>
+        <v>280</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">739173, 5704749</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F22">
-        <v>642</v>
+        <v>849</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">739178, 4460934</t>
+          <t xml:space="preserve">500110, 4464525</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F23">
-        <v>316</v>
+        <v>2773</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">739185, 4452416</t>
+          <t xml:space="preserve">500110, 4464525</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F24">
-        <v>3430</v>
+        <v>2650</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">739186, 1473226</t>
+          <t xml:space="preserve">500111, 4464525</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F25">
-        <v>387</v>
+        <v>325</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">739186, 1473226</t>
+          <t xml:space="preserve">5704296</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F26">
-        <v>421</v>
+        <v>364</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">739202, 4461172</t>
+          <t xml:space="preserve">5704296</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F27">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">739951, 100093371</t>
+          <t xml:space="preserve">5704296</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F28">
-        <v>6652</v>
+        <v>1861</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">739992, 7240937</t>
+          <t xml:space="preserve">5706289</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F29">
-        <v>1626</v>
+        <v>319</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">739992, 7240937</t>
+          <t xml:space="preserve">739159, 5704912</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F30">
-        <v>4117</v>
+        <v>1046</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">739992, 7240937</t>
+          <t xml:space="preserve">739161, 4460928</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>1981</v>
+        <v>983</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">739995, 4506099</t>
+          <t xml:space="preserve">739173, 5704749</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F32">
-        <v>527</v>
+        <v>642</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">739995, 4506099</t>
+          <t xml:space="preserve">739178, 4460934</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F33">
-        <v>2637</v>
+        <v>316</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">739996, 4425111</t>
+          <t xml:space="preserve">739185, 4452416</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F34">
-        <v>2119</v>
+        <v>3430</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">739996, 4425111</t>
+          <t xml:space="preserve">739186, 1473226</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">739998, 4503192</t>
+          <t xml:space="preserve">739186, 1473226</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F36">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">739998, 4503192</t>
+          <t xml:space="preserve">739202, 4461172</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>1423</v>
+        <v>350</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">739999, 4505440</t>
+          <t xml:space="preserve">739951, 100093371</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F38">
-        <v>560</v>
+        <v>6652</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">740050, 4438357</t>
+          <t xml:space="preserve">739995, 4506099</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F39">
-        <v>327</v>
+        <v>2637</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7614785</t>
+          <t xml:space="preserve">739998, 4503192</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F40">
-        <v>299</v>
+        <v>1423</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8771509</t>
+          <t xml:space="preserve">739999, 4505440</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>1064</v>
+        <v>560</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">740050, 4438357</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F42">
-        <v>1327</v>
+        <v>327</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">7614785</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F43">
-        <v>11187</v>
+        <v>299</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">8771509</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F44">
-        <v>7390</v>
+        <v>1064</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,16 +2231,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">9455769</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F45">
-        <v>4622</v>
+        <v>2014</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,30 +2281,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455769</t>
+          <t xml:space="preserve">5704296</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>2014</v>
+        <v>6192</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200038259</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">739996, 4425111</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F47">
-        <v>1164</v>
+        <v>2119</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020000</t>
+          <t xml:space="preserve">200050751</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-07</t>
+          <t xml:space="preserve">2021-06-28</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704296</t>
+          <t xml:space="preserve">739996, 4425111</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F48">
-        <v>6192</v>
+        <v>387</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038259</t>
+          <t xml:space="preserve">200050751</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-01</t>
+          <t xml:space="preserve">2021-06-28</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">739995, 4506099</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>494</v>
+        <v>527</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040171</t>
+          <t xml:space="preserve">200058278</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-01</t>
+          <t xml:space="preserve">2022-03-22</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704296</t>
+          <t xml:space="preserve">739992, 7240937</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F50">
-        <v>734</v>
+        <v>1626</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311193012</t>
+          <t xml:space="preserve">200058535</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-04</t>
+          <t xml:space="preserve">2022-03-29</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,35 +2531,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8647908</t>
+          <t xml:space="preserve">739992, 7240937</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F51">
-        <v>1498</v>
+        <v>4117</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311404533</t>
+          <t xml:space="preserve">200058535</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-18</t>
+          <t xml:space="preserve">2022-03-29</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2581,35 +2581,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">739992, 7240937</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F52">
-        <v>2123</v>
+        <v>1981</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311405290</t>
+          <t xml:space="preserve">200058535</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-23</t>
+          <t xml:space="preserve">2022-03-29</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2631,35 +2631,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">5704296</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F53">
-        <v>1173</v>
+        <v>734</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311405291</t>
+          <t xml:space="preserve">311193012</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-23</t>
+          <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">8647908</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>1193</v>
+        <v>1498</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311405292</t>
+          <t xml:space="preserve">311404533</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-23</t>
+          <t xml:space="preserve">2029-10-18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">10134784</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>2314</v>
+        <v>2123</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408301</t>
+          <t xml:space="preserve">311405290</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2029-10-23</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">10134784</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,16 +2790,16 @@
         </is>
       </c>
       <c r="F56">
-        <v>1059</v>
+        <v>1173</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408289</t>
+          <t xml:space="preserve">311405291</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2029-10-23</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">10134784</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F57">
-        <v>1766</v>
+        <v>1193</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408304</t>
+          <t xml:space="preserve">311405292</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2029-10-23</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,20 +2881,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697088</t>
+          <t xml:space="preserve">10134784</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F58">
-        <v>1234</v>
+        <v>2314</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408309</t>
+          <t xml:space="preserve">311408301</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5695527</t>
+          <t xml:space="preserve">10134784</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F59">
-        <v>459</v>
+        <v>1059</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408670</t>
+          <t xml:space="preserve">311408289</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-13</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5696984</t>
+          <t xml:space="preserve">10134784</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F60">
-        <v>1058</v>
+        <v>1766</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408698</t>
+          <t xml:space="preserve">311408304</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-13</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3036,20 +3036,20 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
-        <v>1206</v>
+        <v>1234</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408665</t>
+          <t xml:space="preserve">311408309</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-13</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,20 +3081,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697088</t>
+          <t xml:space="preserve">5695527</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
-        <v>2872</v>
+        <v>459</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408694</t>
+          <t xml:space="preserve">311408670</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3131,20 +3131,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697088</t>
+          <t xml:space="preserve">5696984</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F63">
-        <v>1146</v>
+        <v>1058</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408667</t>
+          <t xml:space="preserve">311408698</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3186,15 +3186,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F64">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408668</t>
+          <t xml:space="preserve">311408665</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440791</t>
+          <t xml:space="preserve">5697088</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F65">
-        <v>663</v>
+        <v>2872</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411430</t>
+          <t xml:space="preserve">311408694</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-28</t>
+          <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5695566</t>
+          <t xml:space="preserve">5697088</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F66">
-        <v>760</v>
+        <v>1146</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412602</t>
+          <t xml:space="preserve">311408667</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-05</t>
+          <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697332</t>
+          <t xml:space="preserve">5697088</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F67">
-        <v>419</v>
+        <v>1209</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412628</t>
+          <t xml:space="preserve">311408668</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-05</t>
+          <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8140010</t>
+          <t xml:space="preserve">4440791</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="F68">
-        <v>753</v>
+        <v>663</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412603</t>
+          <t xml:space="preserve">311411430</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-05</t>
+          <t xml:space="preserve">2029-11-28</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474174</t>
+          <t xml:space="preserve">5695566</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F69">
-        <v>419</v>
+        <v>760</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414965</t>
+          <t xml:space="preserve">311412602</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-19</t>
+          <t xml:space="preserve">2029-12-05</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4431026</t>
+          <t xml:space="preserve">5697332</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="F70">
-        <v>1364</v>
+        <v>419</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414958</t>
+          <t xml:space="preserve">311412628</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-19</t>
+          <t xml:space="preserve">2029-12-05</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4431026</t>
+          <t xml:space="preserve">8140010</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>930</v>
+        <v>753</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414962</t>
+          <t xml:space="preserve">311412603</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-19</t>
+          <t xml:space="preserve">2029-12-05</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,20 +3581,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440741</t>
+          <t xml:space="preserve">1474174</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F72">
-        <v>735</v>
+        <v>419</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414933</t>
+          <t xml:space="preserve">311414965</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">100086248</t>
+          <t xml:space="preserve">4431026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="F73">
-        <v>363</v>
+        <v>1364</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415880</t>
+          <t xml:space="preserve">311414958</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-06</t>
+          <t xml:space="preserve">2029-12-19</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805469</t>
+          <t xml:space="preserve">4431026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F74">
-        <v>481</v>
+        <v>930</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415890</t>
+          <t xml:space="preserve">311414962</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-06</t>
+          <t xml:space="preserve">2029-12-19</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4465452</t>
+          <t xml:space="preserve">4440741</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F75">
-        <v>520</v>
+        <v>735</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415891</t>
+          <t xml:space="preserve">311414933</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-06</t>
+          <t xml:space="preserve">2029-12-19</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4425050</t>
+          <t xml:space="preserve">100086248</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,16 +3790,16 @@
         </is>
       </c>
       <c r="F76">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416212</t>
+          <t xml:space="preserve">311415880</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-08</t>
+          <t xml:space="preserve">2030-01-06</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433466</t>
+          <t xml:space="preserve">1805469</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,16 +3840,16 @@
         </is>
       </c>
       <c r="F77">
-        <v>1222</v>
+        <v>481</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416210</t>
+          <t xml:space="preserve">311415890</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-08</t>
+          <t xml:space="preserve">2030-01-06</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433875</t>
+          <t xml:space="preserve">4465452</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>645</v>
+        <v>520</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416209</t>
+          <t xml:space="preserve">311415891</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-08</t>
+          <t xml:space="preserve">2030-01-06</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,20 +3931,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433875</t>
+          <t xml:space="preserve">4425050</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>266</v>
+        <v>331</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416208</t>
+          <t xml:space="preserve">311416212</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3981,20 +3981,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4458189</t>
+          <t xml:space="preserve">4433466</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F80">
-        <v>271</v>
+        <v>1222</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416196</t>
+          <t xml:space="preserve">311416210</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8058568</t>
+          <t xml:space="preserve">4433875</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,11 +4040,11 @@
         </is>
       </c>
       <c r="F81">
-        <v>824</v>
+        <v>645</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416199</t>
+          <t xml:space="preserve">311416209</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4086,20 +4086,20 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F82">
-        <v>6406</v>
+        <v>266</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416789</t>
+          <t xml:space="preserve">311416208</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-13</t>
+          <t xml:space="preserve">2030-01-08</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433875</t>
+          <t xml:space="preserve">4458189</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F83">
-        <v>425</v>
+        <v>271</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416802</t>
+          <t xml:space="preserve">311416196</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-13</t>
+          <t xml:space="preserve">2030-01-08</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">8058568</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>746</v>
+        <v>824</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416801</t>
+          <t xml:space="preserve">311416199</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-13</t>
+          <t xml:space="preserve">2030-01-08</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,20 +4231,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4457490</t>
+          <t xml:space="preserve">4433875</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F85">
-        <v>614</v>
+        <v>6406</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416794</t>
+          <t xml:space="preserve">311416789</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4281,20 +4281,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706514</t>
+          <t xml:space="preserve">4433875</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F86">
-        <v>1320</v>
+        <v>425</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416796</t>
+          <t xml:space="preserve">311416802</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4331,20 +4331,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7241642</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F87">
-        <v>1387</v>
+        <v>746</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416785</t>
+          <t xml:space="preserve">311416801</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4381,20 +4381,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8966751</t>
+          <t xml:space="preserve">4457490</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F88">
-        <v>353</v>
+        <v>614</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416792</t>
+          <t xml:space="preserve">311416794</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4460269</t>
+          <t xml:space="preserve">5706514</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F89">
-        <v>277</v>
+        <v>1320</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428990</t>
+          <t xml:space="preserve">311416796</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-19</t>
+          <t xml:space="preserve">2030-01-13</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4460822</t>
+          <t xml:space="preserve">7241642</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="F90">
-        <v>2916</v>
+        <v>1387</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455096</t>
+          <t xml:space="preserve">311416785</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-18</t>
+          <t xml:space="preserve">2030-01-13</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4460822</t>
+          <t xml:space="preserve">4460269</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F91">
-        <v>2366</v>
+        <v>277</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455100</t>
+          <t xml:space="preserve">311428990</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-18</t>
+          <t xml:space="preserve">2030-03-19</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4586,15 +4586,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F92">
-        <v>918</v>
+        <v>2916</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455105</t>
+          <t xml:space="preserve">311455096</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4465145</t>
+          <t xml:space="preserve">4460822</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F93">
-        <v>710</v>
+        <v>2366</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455049</t>
+          <t xml:space="preserve">311455100</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4681,20 +4681,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4465145</t>
+          <t xml:space="preserve">4460822</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F94">
-        <v>306</v>
+        <v>918</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455044</t>
+          <t xml:space="preserve">311455105</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4736,15 +4736,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F95">
-        <v>345</v>
+        <v>710</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455046</t>
+          <t xml:space="preserve">311455049</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4781,20 +4781,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4509182</t>
+          <t xml:space="preserve">4465145</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F96">
-        <v>3093</v>
+        <v>306</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455087</t>
+          <t xml:space="preserve">311455044</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4831,20 +4831,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4510337</t>
+          <t xml:space="preserve">4465145</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F97">
-        <v>1056</v>
+        <v>345</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311455092</t>
+          <t xml:space="preserve">311455046</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">10201137</t>
+          <t xml:space="preserve">4509182</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>800</v>
+        <v>3093</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311456271</t>
+          <t xml:space="preserve">311455087</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-24</t>
+          <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7740155</t>
+          <t xml:space="preserve">4510337</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>310</v>
+        <v>1056</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311456273</t>
+          <t xml:space="preserve">311455092</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-24</t>
+          <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4434708</t>
+          <t xml:space="preserve">7740155</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F102">
-        <v>790</v>
+        <v>310</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461220</t>
+          <t xml:space="preserve">311460443</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-15</t>
+          <t xml:space="preserve">2030-09-11</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4435401</t>
+          <t xml:space="preserve">4434708</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5140,11 +5140,11 @@
         </is>
       </c>
       <c r="F103">
-        <v>1009</v>
+        <v>790</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461221</t>
+          <t xml:space="preserve">311461220</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5181,20 +5181,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4510337</t>
+          <t xml:space="preserve">4435401</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>470</v>
+        <v>1009</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461219</t>
+          <t xml:space="preserve">311461221</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453257</t>
+          <t xml:space="preserve">4510337</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F105">
-        <v>2438</v>
+        <v>470</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311463648</t>
+          <t xml:space="preserve">311461219</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-27</t>
+          <t xml:space="preserve">2030-09-15</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5286,15 +5286,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F106">
-        <v>5782</v>
+        <v>2438</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311463645</t>
+          <t xml:space="preserve">311463648</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5336,15 +5336,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F107">
-        <v>431</v>
+        <v>5782</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311463646</t>
+          <t xml:space="preserve">311463645</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5386,15 +5386,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F108">
-        <v>253</v>
+        <v>431</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311463647</t>
+          <t xml:space="preserve">311463646</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455769</t>
+          <t xml:space="preserve">4453257</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F109">
-        <v>1972</v>
+        <v>253</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464315</t>
+          <t xml:space="preserve">311463647</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-30</t>
+          <t xml:space="preserve">2030-09-27</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455442</t>
+          <t xml:space="preserve">9455769</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5490,16 +5490,16 @@
         </is>
       </c>
       <c r="F110">
-        <v>2812</v>
+        <v>1972</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465122</t>
+          <t xml:space="preserve">311464315</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-04</t>
+          <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5536,15 +5536,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F111">
-        <v>386</v>
+        <v>2812</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465119</t>
+          <t xml:space="preserve">311465122</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455769</t>
+          <t xml:space="preserve">4455442</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F112">
-        <v>1152</v>
+        <v>386</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465344</t>
+          <t xml:space="preserve">311465119</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-05</t>
+          <t xml:space="preserve">2030-10-04</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453257</t>
+          <t xml:space="preserve">4455442, 100194390</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F113">
-        <v>282</v>
+        <v>1173</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471519</t>
+          <t xml:space="preserve">311465121</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-30</t>
+          <t xml:space="preserve">2030-10-04</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462904</t>
+          <t xml:space="preserve">9455769</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F114">
-        <v>380</v>
+        <v>1152</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471529</t>
+          <t xml:space="preserve">311465344</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-30</t>
+          <t xml:space="preserve">2030-10-05</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,20 +5731,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455769</t>
+          <t xml:space="preserve">4453257</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F115">
-        <v>725</v>
+        <v>282</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471524</t>
+          <t xml:space="preserve">311471519</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706289</t>
+          <t xml:space="preserve">4462904</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="F116">
-        <v>7818</v>
+        <v>380</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475497</t>
+          <t xml:space="preserve">311471529</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4506406</t>
+          <t xml:space="preserve">9455769</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F117">
-        <v>498</v>
+        <v>725</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475754</t>
+          <t xml:space="preserve">311471524</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-15</t>
+          <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">5706289</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="F118">
-        <v>2786</v>
+        <v>7818</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480990</t>
+          <t xml:space="preserve">311475497</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8591744</t>
+          <t xml:space="preserve">4506406</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5940,16 +5940,16 @@
         </is>
       </c>
       <c r="F119">
-        <v>3391</v>
+        <v>498</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868826</t>
+          <t xml:space="preserve">311475754</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2030-11-15</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5986,20 +5986,20 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>3979</v>
+        <v>2786</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481616</t>
+          <t xml:space="preserve">311480990</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-09</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,25 +6031,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706491</t>
+          <t xml:space="preserve">8591744</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F121">
-        <v>1380</v>
+        <v>3391</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481632</t>
+          <t xml:space="preserve">311868826</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-09</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704686</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>285</v>
+        <v>3979</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482350</t>
+          <t xml:space="preserve">311481616</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-11</t>
+          <t xml:space="preserve">2030-12-09</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4457628</t>
+          <t xml:space="preserve">5706491</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F123">
-        <v>278</v>
+        <v>1380</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482554</t>
+          <t xml:space="preserve">311481632</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve">2030-12-09</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704845</t>
+          <t xml:space="preserve">5704686</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F124">
-        <v>1208</v>
+        <v>939</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483577</t>
+          <t xml:space="preserve">311482452</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-13</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704845</t>
+          <t xml:space="preserve">5704686</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F125">
-        <v>634</v>
+        <v>285</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483578</t>
+          <t xml:space="preserve">311482452</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-13</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4435005</t>
+          <t xml:space="preserve">4457628</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="F126">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488032</t>
+          <t xml:space="preserve">311482554</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,25 +6331,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">5704845</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F127">
-        <v>482</v>
+        <v>1208</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488095</t>
+          <t xml:space="preserve">311483577</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">5704845</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F128">
-        <v>2078</v>
+        <v>634</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488098</t>
+          <t xml:space="preserve">311483578</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,20 +6431,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">4435005</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F129">
-        <v>1199</v>
+        <v>309</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488100</t>
+          <t xml:space="preserve">311488032</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6481,20 +6481,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F130">
-        <v>1174</v>
+        <v>482</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488103</t>
+          <t xml:space="preserve">311488095</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6536,15 +6536,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F131">
-        <v>587</v>
+        <v>2078</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488102</t>
+          <t xml:space="preserve">311488098</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="F132">
-        <v>3690</v>
+        <v>1199</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500097</t>
+          <t xml:space="preserve">311488100</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6640,16 +6640,16 @@
         </is>
       </c>
       <c r="F133">
-        <v>3682</v>
+        <v>1174</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500098</t>
+          <t xml:space="preserve">311488103</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>1529</v>
+        <v>587</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500100</t>
+          <t xml:space="preserve">311488102</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">5707346</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F138">
-        <v>1438</v>
+        <v>1821</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502543</t>
+          <t xml:space="preserve">311507310</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6936,15 +6936,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F139">
-        <v>1821</v>
+        <v>914</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507310</t>
+          <t xml:space="preserve">311507300</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6986,15 +6986,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F140">
-        <v>914</v>
+        <v>1214</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507300</t>
+          <t xml:space="preserve">311507302</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7036,15 +7036,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F141">
-        <v>1214</v>
+        <v>1296</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507302</t>
+          <t xml:space="preserve">311507304</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7086,15 +7086,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F142">
-        <v>1296</v>
+        <v>1390</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507304</t>
+          <t xml:space="preserve">311507307</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7136,15 +7136,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F143">
-        <v>1390</v>
+        <v>4684</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507307</t>
+          <t xml:space="preserve">311507298</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707346</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F144">
-        <v>4684</v>
+        <v>413</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507298</t>
+          <t xml:space="preserve">311511163</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7236,15 +7236,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F145">
-        <v>413</v>
+        <v>1515</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511163</t>
+          <t xml:space="preserve">311873970</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7286,15 +7286,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F146">
-        <v>1515</v>
+        <v>701</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873970</t>
+          <t xml:space="preserve">311511168</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7336,20 +7336,20 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F147">
-        <v>701</v>
+        <v>1096</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511168</t>
+          <t xml:space="preserve">311511782</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-09</t>
+          <t xml:space="preserve">2031-04-13</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7386,15 +7386,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F148">
-        <v>1096</v>
+        <v>423</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511782</t>
+          <t xml:space="preserve">311511784</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7436,20 +7436,20 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F149">
-        <v>423</v>
+        <v>1052</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511784</t>
+          <t xml:space="preserve">311513130</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-13</t>
+          <t xml:space="preserve">2031-04-16</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">4433294</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F150">
-        <v>1052</v>
+        <v>324</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513130</t>
+          <t xml:space="preserve">311535258</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-16</t>
+          <t xml:space="preserve">2031-07-12</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433294</t>
+          <t xml:space="preserve">4462912</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7540,16 +7540,16 @@
         </is>
       </c>
       <c r="F151">
-        <v>324</v>
+        <v>848</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535258</t>
+          <t xml:space="preserve">311539387</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-12</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462912</t>
+          <t xml:space="preserve">5706491</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="F152">
-        <v>848</v>
+        <v>4954</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539387</t>
+          <t xml:space="preserve">311543939</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706491</t>
+          <t xml:space="preserve">5706423</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,16 +7640,16 @@
         </is>
       </c>
       <c r="F153">
-        <v>4954</v>
+        <v>9030</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543939</t>
+          <t xml:space="preserve">311547312</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-27</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7686,20 +7686,20 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F154">
-        <v>9030</v>
+        <v>802</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547312</t>
+          <t xml:space="preserve">311548281</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706423</t>
+          <t xml:space="preserve">8748212</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F155">
-        <v>802</v>
+        <v>320</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548281</t>
+          <t xml:space="preserve">311549309</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-15</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8748212</t>
+          <t xml:space="preserve">739998, 4503192</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156">
-        <v>320</v>
+        <v>369</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549309</t>
+          <t xml:space="preserve">311553193</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-10-05</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699836</t>
+          <t xml:space="preserve">8966751</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F162">
-        <v>824</v>
+        <v>353</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559406</t>
+          <t xml:space="preserve">311555700</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-03</t>
+          <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8136,15 +8136,15 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F163">
-        <v>617</v>
+        <v>824</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559404</t>
+          <t xml:space="preserve">311559406</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809289</t>
+          <t xml:space="preserve">5699836</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F164">
-        <v>771</v>
+        <v>617</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560386</t>
+          <t xml:space="preserve">311559404</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699836</t>
+          <t xml:space="preserve">1809289</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F165">
-        <v>522</v>
+        <v>771</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566877</t>
+          <t xml:space="preserve">311560386</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8286,15 +8286,15 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F166">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561966</t>
+          <t xml:space="preserve">311566877</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -8336,15 +8336,15 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F167">
-        <v>802</v>
+        <v>525</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561962</t>
+          <t xml:space="preserve">311561966</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8386,15 +8386,15 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F168">
-        <v>472</v>
+        <v>802</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561963</t>
+          <t xml:space="preserve">311561962</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">8966321</t>
+          <t xml:space="preserve">5699836</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F169">
-        <v>615</v>
+        <v>472</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566234</t>
+          <t xml:space="preserve">311561963</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-06</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455731</t>
+          <t xml:space="preserve">8966321</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F170">
-        <v>1001</v>
+        <v>615</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566808</t>
+          <t xml:space="preserve">311566234</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-08</t>
+          <t xml:space="preserve">2031-12-06</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">9455731</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F171">
-        <v>430</v>
+        <v>1001</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567053</t>
+          <t xml:space="preserve">311566808</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-09</t>
+          <t xml:space="preserve">2031-12-08</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">100063131</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F172">
-        <v>1683</v>
+        <v>430</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567248</t>
+          <t xml:space="preserve">311567053</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-10</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433142</t>
+          <t xml:space="preserve">100063131</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8640,16 +8640,16 @@
         </is>
       </c>
       <c r="F173">
-        <v>2469</v>
+        <v>1683</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568010</t>
+          <t xml:space="preserve">311567248</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2031-12-10</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433876</t>
+          <t xml:space="preserve">4433142</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8690,11 +8690,11 @@
         </is>
       </c>
       <c r="F174">
-        <v>2190</v>
+        <v>2469</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568091</t>
+          <t xml:space="preserve">311568010</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">4433876</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="F175">
-        <v>626</v>
+        <v>2190</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568880</t>
+          <t xml:space="preserve">311568091</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">5700031</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F183">
-        <v>825</v>
+        <v>2327</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575940</t>
+          <t xml:space="preserve">311577008</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-02-06</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700031</t>
+          <t xml:space="preserve">5706289</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F184">
-        <v>2327</v>
+        <v>3371</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577008</t>
+          <t xml:space="preserve">311582023</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-06</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F185">
-        <v>514</v>
+        <v>478</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577005</t>
+          <t xml:space="preserve">311582021</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-06</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,20 +9281,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">100377971</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F186">
-        <v>9582</v>
+        <v>453</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582020</t>
+          <t xml:space="preserve">311582022</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706289</t>
+          <t xml:space="preserve">4439896</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F187">
-        <v>3371</v>
+        <v>706</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582023</t>
+          <t xml:space="preserve">311587481</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-23</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F188">
-        <v>478</v>
+        <v>340</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582021</t>
+          <t xml:space="preserve">311587772</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">5704898</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F189">
-        <v>453</v>
+        <v>787</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582022</t>
+          <t xml:space="preserve">311587769</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">334005, 334006, 334007, 334008, 334009, 334010, 334011, 334012, 334013, 334014, 334015, 334016, 334017, 334018, 334019, 334020, 334021, 334022, 334023, 334024, 334025, 334026, 334027, 334028, 334029, 334030, 334036, 334031, 334032, 334033, 334034, 334035, 334037, 334038, 334039, 334040, 334042, 100319954</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F190">
-        <v>9740</v>
+        <v>625</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586771</t>
+          <t xml:space="preserve">311588514</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-21</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,25 +9531,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4439896</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F191">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587481</t>
+          <t xml:space="preserve">311588517</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-23</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">7268351</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F192">
-        <v>340</v>
+        <v>6466</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587772</t>
+          <t xml:space="preserve">311596592</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704898</t>
+          <t xml:space="preserve">4503146</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F193">
-        <v>787</v>
+        <v>347</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587769</t>
+          <t xml:space="preserve">311598021</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,25 +9681,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">5704898</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F194">
-        <v>625</v>
+        <v>15574</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588514</t>
+          <t xml:space="preserve">311598704</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-05-09</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,25 +9731,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">5700242</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F195">
-        <v>738</v>
+        <v>904</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588517</t>
+          <t xml:space="preserve">311599479</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-05-11</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7268351</t>
+          <t xml:space="preserve">5697089</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9790,16 +9790,16 @@
         </is>
       </c>
       <c r="F196">
-        <v>6466</v>
+        <v>1066</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596592</t>
+          <t xml:space="preserve">311601096</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-29</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,25 +9831,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503146</t>
+          <t xml:space="preserve">5702325</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F197">
-        <v>347</v>
+        <v>280</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598021</t>
+          <t xml:space="preserve">311601100</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704898</t>
+          <t xml:space="preserve">5699373</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9890,16 +9890,16 @@
         </is>
       </c>
       <c r="F198">
-        <v>15574</v>
+        <v>1547</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598704</t>
+          <t xml:space="preserve">311604976</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-09</t>
+          <t xml:space="preserve">2032-06-02</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,25 +9931,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700242</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F199">
-        <v>904</v>
+        <v>365</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599479</t>
+          <t xml:space="preserve">311605257</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-11</t>
+          <t xml:space="preserve">2032-06-03</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697089</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9990,16 +9990,16 @@
         </is>
       </c>
       <c r="F200">
-        <v>1066</v>
+        <v>2761</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601096</t>
+          <t xml:space="preserve">311613717</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10031,25 +10031,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5702325</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F201">
-        <v>280</v>
+        <v>1280</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601100</t>
+          <t xml:space="preserve">311613723</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,25 +10081,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699373</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F202">
-        <v>1547</v>
+        <v>1280</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311604976</t>
+          <t xml:space="preserve">311613722</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-02</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10131,25 +10131,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F203">
-        <v>365</v>
+        <v>1280</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605257</t>
+          <t xml:space="preserve">311613720</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-03</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -10190,16 +10190,16 @@
         </is>
       </c>
       <c r="F204">
-        <v>2761</v>
+        <v>2879</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613717</t>
+          <t xml:space="preserve">311614000</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,25 +10231,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F205">
-        <v>1280</v>
+        <v>1084</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613723</t>
+          <t xml:space="preserve">311614001</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,25 +10281,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F206">
-        <v>1280</v>
+        <v>1070</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613722</t>
+          <t xml:space="preserve">311613998</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10331,25 +10331,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">4503146</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F207">
-        <v>1280</v>
+        <v>957</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613720</t>
+          <t xml:space="preserve">311620387</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10381,25 +10381,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">4503146</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F208">
-        <v>2879</v>
+        <v>927</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614000</t>
+          <t xml:space="preserve">311620389</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,25 +10431,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F209">
-        <v>1084</v>
+        <v>1048</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614001</t>
+          <t xml:space="preserve">311620382</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,25 +10481,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">4455105</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F210">
-        <v>1070</v>
+        <v>1524</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613998</t>
+          <t xml:space="preserve">311622235</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,25 +10531,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503146</t>
+          <t xml:space="preserve">4455105</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F211">
-        <v>957</v>
+        <v>1719</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620387</t>
+          <t xml:space="preserve">311622236</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,25 +10581,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503146</t>
+          <t xml:space="preserve">5696550</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F212">
-        <v>927</v>
+        <v>653</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620389</t>
+          <t xml:space="preserve">311623523</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">5707304</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F213">
-        <v>1048</v>
+        <v>8928</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620382</t>
+          <t xml:space="preserve">311628842</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455105</t>
+          <t xml:space="preserve">8279488</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -10690,16 +10690,16 @@
         </is>
       </c>
       <c r="F214">
-        <v>1524</v>
+        <v>860</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622235</t>
+          <t xml:space="preserve">311639214</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-10-31</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,25 +10731,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455105</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F215">
-        <v>1719</v>
+        <v>389</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622236</t>
+          <t xml:space="preserve">311639215</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-10-31</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5696550</t>
+          <t xml:space="preserve">1474174</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F216">
-        <v>653</v>
+        <v>560</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623523</t>
+          <t xml:space="preserve">311643479</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">334871, 334872</t>
+          <t xml:space="preserve">4450791</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -10840,16 +10840,16 @@
         </is>
       </c>
       <c r="F217">
-        <v>2108</v>
+        <v>1852</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623871</t>
+          <t xml:space="preserve">311643477</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-29</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,25 +10881,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707304</t>
+          <t xml:space="preserve">4450791</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F218">
-        <v>8928</v>
+        <v>379</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311628842</t>
+          <t xml:space="preserve">311643496</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8279488</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -10940,16 +10940,16 @@
         </is>
       </c>
       <c r="F219">
-        <v>860</v>
+        <v>2443</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639214</t>
+          <t xml:space="preserve">311649334</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-31</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10981,25 +10981,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F220">
-        <v>389</v>
+        <v>2443</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639215</t>
+          <t xml:space="preserve">311649334</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-31</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474174</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -11040,16 +11040,16 @@
         </is>
       </c>
       <c r="F221">
-        <v>560</v>
+        <v>2011</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643479</t>
+          <t xml:space="preserve">311649334</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450791</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F222">
-        <v>1852</v>
+        <v>2172</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643477</t>
+          <t xml:space="preserve">311644039</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11131,25 +11131,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450791</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F223">
-        <v>379</v>
+        <v>1548</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643496</t>
+          <t xml:space="preserve">311649334</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4425011</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -11190,16 +11190,16 @@
         </is>
       </c>
       <c r="F224">
-        <v>2443</v>
+        <v>1644</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643467</t>
+          <t xml:space="preserve">311646026</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4425011</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -11240,16 +11240,16 @@
         </is>
       </c>
       <c r="F225">
-        <v>2443</v>
+        <v>586</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643464</t>
+          <t xml:space="preserve">311646032</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11281,25 +11281,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4505959</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F226">
-        <v>2011</v>
+        <v>4534</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643469</t>
+          <t xml:space="preserve">311649340</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-12-15</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11331,25 +11331,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4457315</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F227">
-        <v>1548</v>
+        <v>1008</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643474</t>
+          <t xml:space="preserve">311652347</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11381,25 +11381,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4463109</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F228">
-        <v>2172</v>
+        <v>1169</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644039</t>
+          <t xml:space="preserve">311653660</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">4425011</t>
+          <t xml:space="preserve">4462864</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -11440,16 +11440,16 @@
         </is>
       </c>
       <c r="F229">
-        <v>1644</v>
+        <v>724</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646026</t>
+          <t xml:space="preserve">311654163</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11481,25 +11481,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4425011</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F230">
-        <v>586</v>
+        <v>1614</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646032</t>
+          <t xml:space="preserve">311661414</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2033-02-21</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4505959</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -11540,16 +11540,16 @@
         </is>
       </c>
       <c r="F231">
-        <v>4534</v>
+        <v>1980</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649340</t>
+          <t xml:space="preserve">311664324</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-15</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11581,25 +11581,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4457315</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F232">
-        <v>1008</v>
+        <v>1106</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652347</t>
+          <t xml:space="preserve">311664321</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11631,25 +11631,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">4463109</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F233">
-        <v>1169</v>
+        <v>420</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653660</t>
+          <t xml:space="preserve">311664326</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11681,25 +11681,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">329553, 329554</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F234">
-        <v>3790</v>
+        <v>1728</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654167</t>
+          <t xml:space="preserve">311664329</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462864</t>
+          <t xml:space="preserve">8518026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -11740,16 +11740,16 @@
         </is>
       </c>
       <c r="F235">
-        <v>724</v>
+        <v>7138</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654163</t>
+          <t xml:space="preserve">311665603</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">334947, 334948</t>
+          <t xml:space="preserve">4453352</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -11790,16 +11790,16 @@
         </is>
       </c>
       <c r="F236">
-        <v>4340</v>
+        <v>689</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656515</t>
+          <t xml:space="preserve">311698577</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-08-08</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">5697779</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -11840,16 +11840,16 @@
         </is>
       </c>
       <c r="F237">
-        <v>1614</v>
+        <v>1189</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661414</t>
+          <t xml:space="preserve">311698822</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-21</t>
+          <t xml:space="preserve">2033-08-09</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11881,25 +11881,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F238">
-        <v>1980</v>
+        <v>264</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664324</t>
+          <t xml:space="preserve">311702712</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11931,25 +11931,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F239">
-        <v>1106</v>
+        <v>1197</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664321</t>
+          <t xml:space="preserve">311702713</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11981,25 +11981,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F240">
-        <v>420</v>
+        <v>1225</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664326</t>
+          <t xml:space="preserve">311702714</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -12031,25 +12031,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F241">
-        <v>1728</v>
+        <v>825</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664329</t>
+          <t xml:space="preserve">311702715</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">8518026</t>
+          <t xml:space="preserve">5700223</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -12090,16 +12090,16 @@
         </is>
       </c>
       <c r="F242">
-        <v>7138</v>
+        <v>609</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665603</t>
+          <t xml:space="preserve">311704121</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2033-08-31</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453352</t>
+          <t xml:space="preserve">4453567</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -12140,16 +12140,16 @@
         </is>
       </c>
       <c r="F243">
-        <v>689</v>
+        <v>589</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698577</t>
+          <t xml:space="preserve">311704317</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-08</t>
+          <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697779</t>
+          <t xml:space="preserve">100091782</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -12190,16 +12190,16 @@
         </is>
       </c>
       <c r="F244">
-        <v>1189</v>
+        <v>349</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698822</t>
+          <t xml:space="preserve">311712048</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-09</t>
+          <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -12231,25 +12231,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">7740155</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F245">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702712</t>
+          <t xml:space="preserve">311712047</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -12281,25 +12281,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">7952590</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F246">
-        <v>1197</v>
+        <v>308</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702713</t>
+          <t xml:space="preserve">311712050</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12331,25 +12331,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">100595167</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F247">
-        <v>1225</v>
+        <v>410</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702714</t>
+          <t xml:space="preserve">311730337</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12381,25 +12381,25 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">9755163</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F248">
-        <v>825</v>
+        <v>6442</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702715</t>
+          <t xml:space="preserve">311731827</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2034-01-04</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700223</t>
+          <t xml:space="preserve">5699376</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -12440,16 +12440,16 @@
         </is>
       </c>
       <c r="F249">
-        <v>609</v>
+        <v>9550</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704121</t>
+          <t xml:space="preserve">311737634</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-31</t>
+          <t xml:space="preserve">2034-02-07</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -12481,25 +12481,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453567</t>
+          <t xml:space="preserve">10201137</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F250">
-        <v>589</v>
+        <v>800</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704317</t>
+          <t xml:space="preserve">311780365</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-01</t>
+          <t xml:space="preserve">2034-08-26</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">100091782</t>
+          <t xml:space="preserve">100052096</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -12540,16 +12540,16 @@
         </is>
       </c>
       <c r="F251">
-        <v>349</v>
+        <v>11240</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712048</t>
+          <t xml:space="preserve">311784417</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-03</t>
+          <t xml:space="preserve">2034-09-12</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12581,25 +12581,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">7740155</t>
+          <t xml:space="preserve">9949194</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F252">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712047</t>
+          <t xml:space="preserve">311807464</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-03</t>
+          <t xml:space="preserve">2035-01-23</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -12631,25 +12631,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">7952590</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="F253">
-        <v>308</v>
+        <v>1327</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712050</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-03</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12681,25 +12681,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F254">
-        <v>703</v>
+        <v>11187</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729072</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -12731,25 +12731,25 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F255">
-        <v>343</v>
+        <v>7390</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729073</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -12781,25 +12781,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="F256">
-        <v>919</v>
+        <v>4622</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729074</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -12831,25 +12831,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F257">
-        <v>717</v>
+        <v>494</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729075</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -12881,25 +12881,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">100595167</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F258">
-        <v>410</v>
+        <v>1164</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730337</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">9755163</t>
+          <t xml:space="preserve">5697359</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -12940,16 +12940,16 @@
         </is>
       </c>
       <c r="F259">
-        <v>6442</v>
+        <v>5468</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731827</t>
+          <t xml:space="preserve">311837610</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-04</t>
+          <t xml:space="preserve">2035-06-12</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -12981,25 +12981,25 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">332592</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F260">
-        <v>6642</v>
+        <v>496</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733061</t>
+          <t xml:space="preserve">311870967</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-12</t>
+          <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -13031,25 +13031,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699376</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F261">
-        <v>9550</v>
+        <v>514</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737634</t>
+          <t xml:space="preserve">311870967</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-07</t>
+          <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -13086,20 +13086,20 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F262">
-        <v>496</v>
+        <v>825</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780363</t>
+          <t xml:space="preserve">311870967</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-26</t>
+          <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052096</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -13140,16 +13140,16 @@
         </is>
       </c>
       <c r="F263">
-        <v>11240</v>
+        <v>626</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311784417</t>
+          <t xml:space="preserve">311884101</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-12</t>
+          <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -13181,25 +13181,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">9949194</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F264">
-        <v>314</v>
+        <v>3690</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807464</t>
+          <t xml:space="preserve">311884101</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-23</t>
+          <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -13231,25 +13231,25 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697359</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F265">
-        <v>5468</v>
+        <v>3682</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837610</t>
+          <t xml:space="preserve">311884101</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-12</t>
+          <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -13281,25 +13281,25 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">329181</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F266">
-        <v>11385</v>
+        <v>1529</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899308</t>
+          <t xml:space="preserve">311884101</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -13331,25 +13331,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">329484, 329485, 329486, 329487, 329488, 329489, 329490, 329491, 329492, 329510, 329493, 329494, 329495, 329496, 329497, 329498, 329499, 329500, 329502, 329503, 329504, 329505, 329506, 329507, 329508, 329509</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F267">
-        <v>18167</v>
+        <v>1438</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858702</t>
+          <t xml:space="preserve">311884101</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-29</t>
+          <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">

--- a/public/exports/29189919.xlsx
+++ b/public/exports/29189919.xlsx
@@ -6714,7 +6714,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482452</t>
+          <t xml:space="preserve">311482453</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482452</t>
+          <t xml:space="preserve">311482453</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555695</t>
+          <t xml:space="preserve">311555699</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572663</t>
+          <t xml:space="preserve">311572664</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">

--- a/public/exports/29189919.xlsx
+++ b/public/exports/29189919.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L268"/>
+  <dimension ref="A1:M268"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-06-28</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-06-28</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-03-22</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-03-29</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-03-29</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-03-29</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-18</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-23</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-23</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-23</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-13</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-28</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-05</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-05</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-05</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-19</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-19</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-19</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-19</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-06</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-06</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-06</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-08</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-08</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-08</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-08</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-08</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-08</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-13</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-13</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-13</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-13</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-13</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-13</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-19</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-18</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-11</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-11</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-11</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-15</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-15</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-15</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-27</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-27</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-27</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-27</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-30</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-04</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-04</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-04</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-05</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6414,20 +6944,25 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475754</t>
+          <t xml:space="preserve">311475755</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-15</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-09</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-09</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6714,20 +7269,25 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482453</t>
+          <t xml:space="preserve">311482452</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-13</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6774,20 +7334,25 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482453</t>
+          <t xml:space="preserve">311482452</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-13</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-13</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-13</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-16</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-12</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Graugaard Consult aps</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-05</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-06</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-13</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-06</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-08</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-10</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9954,20 +10779,25 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572664</t>
+          <t xml:space="preserve">311572663</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-17</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-06</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-23</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10674,20 +11559,25 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587769</t>
+          <t xml:space="preserve">311587770</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-09</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-11</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-02</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-03</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-29</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-31</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-31</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12714,20 +13769,25 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644039</t>
+          <t xml:space="preserve">311649334</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-15</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-21</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-08</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-09</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-31</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-04</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-12</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-07</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-26</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-12</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-23</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-12</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15479,15 +16764,20 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-29</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15599,15 +16894,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,15 +17154,20 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15899,15 +17219,20 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15959,15 +17284,20 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16019,15 +17349,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16079,21 +17414,26 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiTjenesten</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L268" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L268"/>
+  <autoFilter ref="A1:M268"/>
 </worksheet>
 </file>
--- a/public/exports/29189919.xlsx
+++ b/public/exports/29189919.xlsx
@@ -6944,7 +6944,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475755</t>
+          <t xml:space="preserve">311475754</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555699</t>
+          <t xml:space="preserve">311555695</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587770</t>
+          <t xml:space="preserve">311587769</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649334</t>
+          <t xml:space="preserve">311644039</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
